--- a/referral_form_templates/040_inventory_specialist_referral_form--referral_form_templates.xlsx
+++ b/referral_form_templates/040_inventory_specialist_referral_form--referral_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>contact_name</t>
+          <t>contact_name_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Contact name</t>
+          <t>Contact Name 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'job_1',_'value':_'job_1'}</t>
+          <t>job_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Job 1', 'value': 'job_1'}</t>
+          <t>Job 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'job_2',_'value':_'job_2'}</t>
+          <t>job_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Job 2', 'value': 'job_2'}</t>
+          <t>Job 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'job_3',_'value':_'job_3'}</t>
+          <t>job_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Job 3', 'value': 'job_3'}</t>
+          <t>Job 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Open', 'value': 'open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'filled',_'value':_'filled'}</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Filled', 'value': 'filled'}</t>
+          <t>Filled</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Closed', 'value': 'closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'user_1',_'value':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'User 1', 'value': 'user_1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'user_2',_'value':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'User 2', 'value': 'user_2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'user_1',_'value':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'User 1', 'value': 'user_1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'user_2',_'value':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'User 2', 'value': 'user_2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
